--- a/data/daily/2026-10/2026-10-25.xlsx
+++ b/data/daily/2026-10/2026-10-25.xlsx
@@ -1193,14 +1193,64 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1215,17 +1265,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1240,17 +1315,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1265,110 +1365,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1448,182 +1448,182 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="866775" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -2084,22 +2084,22 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16346</v>
+        <v>16347</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 증진 — 피로가 달아나고 힘이 나는 효과를 경험함.</t>
+          <t>피로 회복 및 건강 개선 — 피로가 풀리고 힘이 나며 입술 터짐 및 감기 회복에 도움이 됨</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>선물용으로 매우 적합 — 출산, 답례품, 응원 등 다양한 선물용으로 적합함.</t>
+          <t>부담 없는 선물용 — 답례품이나 응원 선물로 주고받기 유용함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>원산지 표기 아쉬움 — 원산지 표기가 표지 앞뒤에 정확하게 표시되었으면 함.</t>
+          <t>원산지 표시 위치 아쉬움 — 원산지가 표지면 앞뒤에 정확히 표시되면 좋겠다는 의견이 있음</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2143,21 +2143,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15685</v>
+        <v>15686</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>피로 개선 효과 — 야근 및 환절기 피로감을 완화하는 데 도움을 줌.</t>
+          <t>우수한 피로 회복 효과 — 야근이나 환절기 피로 개선에 높은 효과를 느낌</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 섭취와 배송 — 비타민을 간편히 챙길 수 있고 빠른 배송을 제공함.</t>
+          <t>세련된 패키지와 섭취 편의 — 패키지가 세련되고 알약과 액상이 함께 있어 복용이 간편함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>지인 응원 선물 — 지인에게 부담 없이 마음을 전하는 응원 선물로 좋음.</t>
+          <t>안전하고 빠른 배송 — 배송이 안전하고 빠르게 전달됨</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2206,17 +2206,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 — 체력이 달릴 때 에너지를 불어넣어 주고 기운이 남.</t>
+          <t>에너지 및 피로 개선 — 체력이 떨어지거나 지칠 때 섭취하면 힘이 확실히 남</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>선물 선호도 높음 — 유명 영양제로 생일이나 회갑 선물용 만족도가 높음.</t>
+          <t>높은 선물 만족도 — 고급스럽고 유명하여 선물받았을 때 기분이 좋음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>진한 농도와 편안함 — 액상 농도가 진하고 섭취 시 속이 편안함.</t>
+          <t>진한 액상 농도 — 타 액상 비타민에 비해 농도가 확실히 진함</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2265,23 +2265,23 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있고 쫄깃한 식감 — 새콤달콤하고 적당히 말랑하여 맛있게 먹을 수 있음.</t>
+          <t>맛있고 쫄깃한 구미 — 새콤달콤하고 적당히 말랑하며 쫄깃해서 맛이 좋음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 구미 형태 — 물 없이 씹어 먹는 젤리 형태라 챙겨 먹기 간편함.</t>
+          <t>물 없이 간편한 섭취 — 구미 형태라 바쁜 아침에도 물 없이 간편하게 먹기 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>포장 개봉의 불편함 — 밀봉 포장이 잘 뜯어지지 않아 개봉하기 힘듦.</t>
+          <t>개봉이 어려운 포장 — 제품 포장이 잘 뜯어지지 않아 개봉 시 인내심이 필요함</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>어린이 비타민 느낌 — 하리보 같아서 성인용 영양제 느낌이 다소 부족함.</t>
+          <t>간식 같은 비타민 제형 — 비타민보다는 하리보나 아이들 간식을 먹는 느낌이 듦</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -2328,19 +2328,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>피로 회복 효과 — 피로 회복에 도움을 주고 상쾌한 느낌을 줌.</t>
+          <t>뛰어난 피로 회복 — 피로 회복 효과가 우수하며 몸과 마음이 상쾌해짐</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>휴대와 섭취 편의성 — 섭취와 휴대가 편해 일상에서 잘 챙겨 먹게 됨.</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>센스 있는 선물 — 환절기나 생일에 챙겨주기 좋은 센스 있는 선물임.</t>
-        </is>
-      </c>
+          <t>편리한 휴대 및 섭취 — 복용이 편하고 휴대하기 좋아 일상에서 챙겨 먹기 적합함</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2387,22 +2383,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 패키지가 고급스럽고 쇼핑백을 함께 제공해 선물용으로 좋음.</t>
+          <t>고급스러운 포장과 배송 — 포장이 깔끔하고 고급스러우며 다음 날 바로 도착함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>재미있는 섭취 방식 — 버튼을 눌러 섞어 마시는 재미가 있고 망고 맛이 남.</t>
+          <t>달콤한 맛과 섞는 재미 — 신맛이 적고 달콤한 망고 맛이며 버튼을 눌러 섞어 먹는 방식이 재밌음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>컨디션 개선 효과 — 마시고 나면 컨디션이 좋아지는 효과가 느껴짐.</t>
+          <t>컨디션 향상 효과 — 아침마다 섭취 시 확실히 컨디션이 좋아짐을 느낌</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>포장 개봉의 어려움 — 버튼이 뻑뻑하고 비닐을 벗기기 어려워 어르신에게 불편함.</t>
+          <t>용기 개봉의 불편함 — 버튼이 뻑뻑하고 비닐 포장을 벗기기가 어려워 어르신에게 불편할 수 있음</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2450,19 +2446,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>아침 피로 회복 — 피곤할 때 먹고 출근하면 기운을 차릴 수 있음.</t>
+          <t>빠른 피로 회복 효과 — 피곤한 아침에 먹고 출근하면 기운이 나고 힘이 생김</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>액상 섭취의 편의성 — 마시는 액상 형태라 간편하게 섭취할 수 있음.</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>빠른 배송 및 선물 — 배송이 빠르고 건강을 챙겨주는 선물용으로 적합함.</t>
-        </is>
-      </c>
+          <t>액상 제형의 섭취 편의 — 마시는 액상 형태라 섭취하기 간편함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -2509,18 +2501,18 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>확실한 활력 충전 — 바쁜 일상에서 피로를 줄이고 확실한 활력을 줌.</t>
+          <t>확실한 활력 제공 — 바쁜 일상이나 피로할 때 확실한 활력과 효과를 체감함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>섭취 및 선물 편의 — 먹기 편하고 효과가 뛰어나 선물하기 좋음.</t>
+          <t>편리한 섭취와 배송 — 먹기 편하고 배송 상태가 양호함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>아쉬운 맛 평가 — 오렌지 맛 감기약 느낌이 나서 맛은 호불호가 갈림.</t>
+          <t>아쉬운 제품 맛 — 오렌지 맛 감기약 느낌이 나서 맛있다 느끼기 어려움</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -2568,18 +2560,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>고함량 비타민C — 메가도스C 3000 함량으로 몸이 리프레쉬됨.</t>
+          <t>활력 제공 및 체력 증진 — 복용 시 리프레쉬되는 느낌이 들고 고용량이라 효과적임</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>휴대성 및 선물용 — 가방에 넣고 다니기 좋고 주변 선물용으로 제격임.</t>
+          <t>간편한 휴대성 — 가방에 넣어 다니며 챙겨 먹기 편리함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>물 없이 섭취 시 신맛 — 물 없이 분말만 복용할 경우 강한 신맛이 남.</t>
+          <t>매우 강한 신맛 — 신맛이 매우 어마어마하여 반드시 물과 함께 섭취해야 함</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -2627,22 +2619,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>편리한 개별 포장 — 개별 포장되어 있어 깔끔하고 휴대 및 섭취가 간편함.</t>
+          <t>한 포 개별 포장의 편의 — 한 팩 개별 포장이라 깔끔하고 휴대와 섭취가 편리함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>활력 증진 효과 — 24종 기능성을 담아 복용 시 힘이 나는 느낌을 받음.</t>
+          <t>피로 개선 및 영양 충전 — 꾸준히 복용 시 힘이 나며 24종 기능성을 담아 만족스러움</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 패키징이 고급스러워 감동을 주는 선물용으로 좋음.</t>
+          <t>고급스러운 포장 — 패키징이 고급스럽고 포장이 깔끔함</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>아쉬운 사은품 품질 — 동봉된 사은품이 다이소 판매 제품이라 다소 아쉬움.</t>
+          <t>사은품 품질 아쉬움 — 동봉된 사은품이 다이소 판매 제품이라 다소 아쉬움</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -2686,21 +2678,21 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 할인가나 톡딜 구매 시 저렴하게 득템할 수 있음.</t>
+          <t>뛰어난 가성비 — 할인가로 저렴하게 구매할 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>풍성한 사은품 — 저당견과류바, 단백칩 등 다채로운 증정품을 함께 제공함.</t>
+          <t>풍성한 사은품 제공 — 견과류 바 등 다양한 사은품이 함께 증정됨</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>달콤하고 편한 맛 — 달콤하여 부담 없이 매일 챙겨 먹기 편함.</t>
+          <t>달콤하고 편한 섭취 — 달콤한 맛이라 먹기 편하며 소화 효과가 우수함</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2749,17 +2741,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>탁월한 숙취 해소 — 음주 전후 섭취 시 두통이 줄고 숙취 완화에 효과적임.</t>
+          <t>확실한 숙취 해소 — 음주 전후 섭취 시 다음 날 숙취와 두통이 줄어듦</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>휴대하기 편한 형태 — 스틱 형태 액상이라 보관 및 휴대가 편리함.</t>
+          <t>스틱 액상형의 휴대성 — 스틱 개별 포장이라 휴대하기 좋고 물 없이 바로 마실 수 있음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>거부감 없는 맛 — 맛이 달콤하고 텁텁하지 않아 쉽게 먹을 수 있음.</t>
+          <t>거부감 없는 달콤함 — 달콤하고 맛이 좋아 거부감 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2808,20 +2800,20 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>다양한 맛 구성 — 맛 종류가 다채로워 식단 관리 중에도 질리지 않음.</t>
+          <t>다양하고 맛있는 구성 — 다양한 맛으로 구성되어 질리지 않고 맛있게 식단 관리가 가능함</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>부드럽고 촉촉함 — 닭가슴살 살이 부드럽고 촉촉함.</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>신속한 누락 대처 — 수량 누락 문의 시 즉시 재발송해 줌.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>부드러운 식감과 편의성 — 닭가슴살이 부드럽고 간단히 데워 먹기 편리함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>배송 누락 발생 — 구성품 수량이 일부 누락되어 수령하는 경우가 발생함</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -2867,22 +2859,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>소화 개선 효과 — 식후 더부룩함이 감소하고 속이 편안해짐.</t>
+          <t>우수한 소화 개선 효과 — 식사 후 더부룩할 때 먹으면 속이 편안해짐</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>고소한 미숫가루 맛 — 미숫가루처럼 고소하고 텁텁하지 않음.</t>
+          <t>고소한 미숫가루 맛 — 텁텁하지 않고 미숫가루처럼 고소함</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>알찬 구성 및 포장 — 고급 포장과 견과류바 등 푸짐한 사은품을 증정함.</t>
+          <t>고급 포장과 알찬 구성 — 선물용 포장이 고급스럽고 견과류 바 등 사은품 구성이 좋음</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>이벤트 쿠폰 확인 불편 — 기프티콘 혜택 확인 위치가 불명확함.</t>
+          <t>기프티콘 안내 부족 — 증정 기프티콘 확인 방법에 대한 안내가 불명확함</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -2930,27 +2922,27 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>흰자 구성 및 편리성 — 계란 흰자만 있어 껍질 끌 필요 없이 섭취가 간편함.</t>
+          <t>퍽퍽함 없는 흰자 구성 — 노른자 없이 흰자로만 되어 있어 비리지 않고 퍽퍽하지 않음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>비린 맛없는 깔끔함 — 계란 특유의 비린 맛이 없고 짭짤하여 맛있음.</t>
+          <t>껍질 없는 간편함 — 계란 껍질을 끌 필요가 없어 언제 어디서나 먹기 좋음</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>다이어트 간식 적합 — 칼로리가 낮고 포만감이 잘 유지됨.</t>
+          <t>부담 없는 칼로리 — 칼로리 부담이 적고 포만감이 오래 지속됨</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>포장 박스 상태 아쉬움 — 배송용 박스 외관 상태가 다소 깨끗하지 않음.</t>
+          <t>혼합 구성의 부재 — 여러 맛을 한 번에 맛볼 수 있는 혼합 구성이 없음</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>단일 맛 구성의 아쉬움 — 다양한 맛을 조합한 혼합 상품 옵션이 없음.</t>
+          <t>택배 박스 상태 아쉬움 — 배송 박스가 깨끗하지 않은 재활용 상자처럼 도착함</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -2958,7 +2950,7 @@
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2966,50 +2958,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>278</v>
+        <v>71</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>우수한 맛 선택지 — 소다, 쿠키앤크림 맛이 뛰어나 먹기 좋음.</t>
+          <t>촉촉하고 맛있는 식감 — 퍽퍽하지 않고 아주 촉촉하며 특색 있는 소스 맛이 훌륭함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>만족스러운 증정품 — 포토카드, 엽서, 단백질바 등 알찬 구성을 제공함.</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>과식 후 소화 도움 — 과식했을 때 먹으면 소화 효과가 느껴짐.</t>
-        </is>
-      </c>
+          <t>간편한 조리 방식 — 전자레인지로 간편하게 데워 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -3017,7 +3005,7 @@
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3025,50 +3013,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>71</v>
+        <v>278</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 맛 — 닭가슴살이 촉촉하고 다양한 맛이 있어 질리지 않음.</t>
+          <t>맛있는 다양한 맛 — 쿠키앤크림, 소다아이스크림 등 거부감 없이 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>간편한 전자레인지 조리 — 전자레인지에 간편히 데워 먹기 좋음.</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>빠르고 튼튼한 배송 — 배송이 빠르고 튼튼하게 포장되어 도착함.</t>
-        </is>
-      </c>
+          <t>알찬 아이돌 굿즈 구성 — 포토카드, 엽서 등 팬들을 위한 알찬 구성품이 제공됨</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -3115,26 +3099,30 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>다양한 맛과 가성비 — 떡볶이맛 등 구성이 다채롭고 할인가 구매 시 만족스러움.</t>
+          <t>맛있는 소스 닭가슴살 — 떡볶이 맛 등 소스 맛이 뛰어나 가성비 높게 즐길 수 있음</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>식단 패키지 구성 — 한 달 식단 패키지로 여러 닭가슴살을 접할 수 있음.</t>
+          <t>실용적인 보냉백 증정 — 사은품으로 제공되는 보냉 가방의 디자인이 예쁘고 실용적임</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>배송 누락 및 임의 대체 — 수량 누락과 임의 상품 대체가 발생하고 처리가 늦음.</t>
+          <t>수량 누락 및 임의 대체 — 수량 불일치 및 사전 고지 없는 대체품 배송으로 스트레스를 유발함</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>강한 간과 가격 부담 — 간이 다소 세고 구성 대비 가격이 비싸게 느껴짐.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>자극적인 센 간 — 일부 제품의 간이 다소 세게 느껴짐</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>배송 중 일부 해동 — 배송 시 제품이 약간 녹아서 도착함</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
@@ -3178,17 +3166,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 플리츠백 등 패키지가 고급스러워 선물 받기 좋음.</t>
+          <t>고급스러운 선물 포장 — 패키지와 플리츠백 구성이 고급스러워 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>맛있고 간편한 앰플 — 맛이 좋고 하루 한 병씩 마시는 앰플 형태라 편리함.</t>
+          <t>맛있고 간편한 복용 — 맛이 좋고 앰플 형태로 되어 있어 간편하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>피부 상태 개선 기대 — 촉촉한 피부 유지와 탄력 관리에 도움을 줌.</t>
+          <t>피부 보습 효과 — 섭취 시 피부가 촉촉해지는 것을 느낌</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3237,17 +3225,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>비린 맛없는 우수한 맛 — 딸기초코 등 비린 맛이 없고 음료수처럼 맛있음.</t>
+          <t>비린 맛 없는 달콤함 — 단백질 특유의 비린 맛이 없고 일반 음료처럼 맛있음</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>운동 후 포만감 제공 — 운동 후 섭취하면 은근히 배가 차고 포만감이 생김.</t>
+          <t>든든한 포만감 제공 — 마시고 나면 배가 든든하여 간식 대용으로 유용함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>선물용 인지도 높음 — 운동하는 지인이나 부모님 선물용으로 추천받음.</t>
+          <t>운동 후 단백질 보충 — 운동 후 한 포씩 챙겨 마시기 편리함</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3572,10 +3560,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16346</v>
+        <v>16347</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15685</v>
+        <v>15686</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3425</v>
@@ -3610,68 +3598,66 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 증진 — 피로가 달아나고 힘이 나는 효과를 경험함.
-선물용으로 매우 적합 — 출산, 답례품, 응원 등 다양한 선물용으로 적합함.</t>
+          <t>피로 회복 및 건강 개선 — 피로가 풀리고 힘이 나며 입술 터짐 및 감기 회복에 도움이 됨
+부담 없는 선물용 — 답례품이나 응원 선물로 주고받기 유용함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>피로 개선 효과 — 야근 및 환절기 피로감을 완화하는 데 도움을 줌.
-간편한 섭취와 배송 — 비타민을 간편히 챙길 수 있고 빠른 배송을 제공함.
-지인 응원 선물 — 지인에게 부담 없이 마음을 전하는 응원 선물로 좋음.</t>
+          <t>우수한 피로 회복 효과 — 야근이나 환절기 피로 개선에 높은 효과를 느낌
+세련된 패키지와 섭취 편의 — 패키지가 세련되고 알약과 액상이 함께 있어 복용이 간편함
+안전하고 빠른 배송 — 배송이 안전하고 빠르게 전달됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 — 체력이 달릴 때 에너지를 불어넣어 주고 기운이 남.
-선물 선호도 높음 — 유명 영양제로 생일이나 회갑 선물용 만족도가 높음.
-진한 농도와 편안함 — 액상 농도가 진하고 섭취 시 속이 편안함.</t>
+          <t>에너지 및 피로 개선 — 체력이 떨어지거나 지칠 때 섭취하면 힘이 확실히 남
+높은 선물 만족도 — 고급스럽고 유명하여 선물받았을 때 기분이 좋음
+진한 액상 농도 — 타 액상 비타민에 비해 농도가 확실히 진함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있고 쫄깃한 식감 — 새콤달콤하고 적당히 말랑하여 맛있게 먹을 수 있음.
-간편한 구미 형태 — 물 없이 씹어 먹는 젤리 형태라 챙겨 먹기 간편함.</t>
+          <t>맛있고 쫄깃한 구미 — 새콤달콤하고 적당히 말랑하며 쫄깃해서 맛이 좋음
+물 없이 간편한 섭취 — 구미 형태라 바쁜 아침에도 물 없이 간편하게 먹기 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 효과 — 피로 회복에 도움을 주고 상쾌한 느낌을 줌.
-휴대와 섭취 편의성 — 섭취와 휴대가 편해 일상에서 잘 챙겨 먹게 됨.
-센스 있는 선물 — 환절기나 생일에 챙겨주기 좋은 센스 있는 선물임.</t>
+          <t>뛰어난 피로 회복 — 피로 회복 효과가 우수하며 몸과 마음이 상쾌해짐
+편리한 휴대 및 섭취 — 복용이 편하고 휴대하기 좋아 일상에서 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 패키지가 고급스럽고 쇼핑백을 함께 제공해 선물용으로 좋음.
-재미있는 섭취 방식 — 버튼을 눌러 섞어 마시는 재미가 있고 망고 맛이 남.
-컨디션 개선 효과 — 마시고 나면 컨디션이 좋아지는 효과가 느껴짐.</t>
+          <t>고급스러운 포장과 배송 — 포장이 깔끔하고 고급스러우며 다음 날 바로 도착함
+달콤한 맛과 섞는 재미 — 신맛이 적고 달콤한 망고 맛이며 버튼을 눌러 섞어 먹는 방식이 재밌음
+컨디션 향상 효과 — 아침마다 섭취 시 확실히 컨디션이 좋아짐을 느낌</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>아침 피로 회복 — 피곤할 때 먹고 출근하면 기운을 차릴 수 있음.
-액상 섭취의 편의성 — 마시는 액상 형태라 간편하게 섭취할 수 있음.
-빠른 배송 및 선물 — 배송이 빠르고 건강을 챙겨주는 선물용으로 적합함.</t>
+          <t>빠른 피로 회복 효과 — 피곤한 아침에 먹고 출근하면 기운이 나고 힘이 생김
+액상 제형의 섭취 편의 — 마시는 액상 형태라 섭취하기 간편함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>확실한 활력 충전 — 바쁜 일상에서 피로를 줄이고 확실한 활력을 줌.
-섭취 및 선물 편의 — 먹기 편하고 효과가 뛰어나 선물하기 좋음.</t>
+          <t>확실한 활력 제공 — 바쁜 일상이나 피로할 때 확실한 활력과 효과를 체감함
+편리한 섭취와 배송 — 먹기 편하고 배송 상태가 양호함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>고함량 비타민C — 메가도스C 3000 함량으로 몸이 리프레쉬됨.
-휴대성 및 선물용 — 가방에 넣고 다니기 좋고 주변 선물용으로 제격임.</t>
+          <t>활력 제공 및 체력 증진 — 복용 시 리프레쉬되는 느낌이 들고 고용량이라 효과적임
+간편한 휴대성 — 가방에 넣어 다니며 챙겨 먹기 편리함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>편리한 개별 포장 — 개별 포장되어 있어 깔끔하고 휴대 및 섭취가 간편함.
-활력 증진 효과 — 24종 기능성을 담아 복용 시 힘이 나는 느낌을 받음.
-고급스러운 패키지 — 패키징이 고급스러워 감동을 주는 선물용으로 좋음.</t>
+          <t>한 포 개별 포장의 편의 — 한 팩 개별 포장이라 깔끔하고 휴대와 섭취가 편리함
+피로 개선 및 영양 충전 — 꾸준히 복용 시 힘이 나며 24종 기능성을 담아 만족스러움
+고급스러운 포장 — 패키징이 고급스럽고 포장이 깔끔함</t>
         </is>
       </c>
     </row>
@@ -3683,37 +3669,37 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>원산지 표기 아쉬움 — 원산지 표기가 표지 앞뒤에 정확하게 표시되었으면 함.</t>
+          <t>원산지 표시 위치 아쉬움 — 원산지가 표지면 앞뒤에 정확히 표시되면 좋겠다는 의견이 있음</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>포장 개봉의 불편함 — 밀봉 포장이 잘 뜯어지지 않아 개봉하기 힘듦.
-어린이 비타민 느낌 — 하리보 같아서 성인용 영양제 느낌이 다소 부족함.</t>
+          <t>개봉이 어려운 포장 — 제품 포장이 잘 뜯어지지 않아 개봉 시 인내심이 필요함
+간식 같은 비타민 제형 — 비타민보다는 하리보나 아이들 간식을 먹는 느낌이 듦</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>포장 개봉의 어려움 — 버튼이 뻑뻑하고 비닐을 벗기기 어려워 어르신에게 불편함.</t>
+          <t>용기 개봉의 불편함 — 버튼이 뻑뻑하고 비닐 포장을 벗기기가 어려워 어르신에게 불편할 수 있음</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 맛 평가 — 오렌지 맛 감기약 느낌이 나서 맛은 호불호가 갈림.</t>
+          <t>아쉬운 제품 맛 — 오렌지 맛 감기약 느낌이 나서 맛있다 느끼기 어려움</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>물 없이 섭취 시 신맛 — 물 없이 분말만 복용할 경우 강한 신맛이 남.</t>
+          <t>매우 강한 신맛 — 신맛이 매우 어마어마하여 반드시 물과 함께 섭취해야 함</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 사은품 품질 — 동봉된 사은품이 다이소 판매 제품이라 다소 아쉬움.</t>
+          <t>사은품 품질 아쉬움 — 동봉된 사은품이 다이소 판매 제품이라 다소 아쉬움</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3924,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -3995,12 +3981,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -4052,12 +4038,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
           <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -4120,7 +4106,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>111</v>
@@ -4135,10 +4121,10 @@
         <v>33</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>278</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>71</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>162</v>
@@ -4158,75 +4144,72 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 할인가나 톡딜 구매 시 저렴하게 득템할 수 있음.
-풍성한 사은품 — 저당견과류바, 단백칩 등 다채로운 증정품을 함께 제공함.
-달콤하고 편한 맛 — 달콤하여 부담 없이 매일 챙겨 먹기 편함.</t>
+          <t>뛰어난 가성비 — 할인가로 저렴하게 구매할 수 있어 만족스러움
+풍성한 사은품 제공 — 견과류 바 등 다양한 사은품이 함께 증정됨
+달콤하고 편한 섭취 — 달콤한 맛이라 먹기 편하며 소화 효과가 우수함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>탁월한 숙취 해소 — 음주 전후 섭취 시 두통이 줄고 숙취 완화에 효과적임.
-휴대하기 편한 형태 — 스틱 형태 액상이라 보관 및 휴대가 편리함.
-거부감 없는 맛 — 맛이 달콤하고 텁텁하지 않아 쉽게 먹을 수 있음.</t>
+          <t>확실한 숙취 해소 — 음주 전후 섭취 시 다음 날 숙취와 두통이 줄어듦
+스틱 액상형의 휴대성 — 스틱 개별 포장이라 휴대하기 좋고 물 없이 바로 마실 수 있음
+거부감 없는 달콤함 — 달콤하고 맛이 좋아 거부감 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>다양한 맛 구성 — 맛 종류가 다채로워 식단 관리 중에도 질리지 않음.
-부드럽고 촉촉함 — 닭가슴살 살이 부드럽고 촉촉함.
-신속한 누락 대처 — 수량 누락 문의 시 즉시 재발송해 줌.</t>
+          <t>다양하고 맛있는 구성 — 다양한 맛으로 구성되어 질리지 않고 맛있게 식단 관리가 가능함
+부드러운 식감과 편의성 — 닭가슴살이 부드럽고 간단히 데워 먹기 편리함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>소화 개선 효과 — 식후 더부룩함이 감소하고 속이 편안해짐.
-고소한 미숫가루 맛 — 미숫가루처럼 고소하고 텁텁하지 않음.
-알찬 구성 및 포장 — 고급 포장과 견과류바 등 푸짐한 사은품을 증정함.</t>
+          <t>우수한 소화 개선 효과 — 식사 후 더부룩할 때 먹으면 속이 편안해짐
+고소한 미숫가루 맛 — 텁텁하지 않고 미숫가루처럼 고소함
+고급 포장과 알찬 구성 — 선물용 포장이 고급스럽고 견과류 바 등 사은품 구성이 좋음</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>흰자 구성 및 편리성 — 계란 흰자만 있어 껍질 끌 필요 없이 섭취가 간편함.
-비린 맛없는 깔끔함 — 계란 특유의 비린 맛이 없고 짭짤하여 맛있음.
-다이어트 간식 적합 — 칼로리가 낮고 포만감이 잘 유지됨.</t>
+          <t>퍽퍽함 없는 흰자 구성 — 노른자 없이 흰자로만 되어 있어 비리지 않고 퍽퍽하지 않음
+껍질 없는 간편함 — 계란 껍질을 끌 필요가 없어 언제 어디서나 먹기 좋음
+부담 없는 칼로리 — 칼로리 부담이 적고 포만감이 오래 지속됨</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>우수한 맛 선택지 — 소다, 쿠키앤크림 맛이 뛰어나 먹기 좋음.
-만족스러운 증정품 — 포토카드, 엽서, 단백질바 등 알찬 구성을 제공함.
-과식 후 소화 도움 — 과식했을 때 먹으면 소화 효과가 느껴짐.</t>
+          <t>촉촉하고 맛있는 식감 — 퍽퍽하지 않고 아주 촉촉하며 특색 있는 소스 맛이 훌륭함
+간편한 조리 방식 — 전자레인지로 간편하게 데워 먹을 수 있음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 맛 — 닭가슴살이 촉촉하고 다양한 맛이 있어 질리지 않음.
-간편한 전자레인지 조리 — 전자레인지에 간편히 데워 먹기 좋음.
-빠르고 튼튼한 배송 — 배송이 빠르고 튼튼하게 포장되어 도착함.</t>
+          <t>맛있는 다양한 맛 — 쿠키앤크림, 소다아이스크림 등 거부감 없이 맛있게 먹을 수 있음
+알찬 아이돌 굿즈 구성 — 포토카드, 엽서 등 팬들을 위한 알찬 구성품이 제공됨</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>다양한 맛과 가성비 — 떡볶이맛 등 구성이 다채롭고 할인가 구매 시 만족스러움.
-식단 패키지 구성 — 한 달 식단 패키지로 여러 닭가슴살을 접할 수 있음.</t>
+          <t>맛있는 소스 닭가슴살 — 떡볶이 맛 등 소스 맛이 뛰어나 가성비 높게 즐길 수 있음
+실용적인 보냉백 증정 — 사은품으로 제공되는 보냉 가방의 디자인이 예쁘고 실용적임</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 플리츠백 등 패키지가 고급스러워 선물 받기 좋음.
-맛있고 간편한 앰플 — 맛이 좋고 하루 한 병씩 마시는 앰플 형태라 편리함.
-피부 상태 개선 기대 — 촉촉한 피부 유지와 탄력 관리에 도움을 줌.</t>
+          <t>고급스러운 선물 포장 — 패키지와 플리츠백 구성이 고급스러워 선물용으로 훌륭함
+맛있고 간편한 복용 — 맛이 좋고 앰플 형태로 되어 있어 간편하게 먹을 수 있음
+피부 보습 효과 — 섭취 시 피부가 촉촉해지는 것을 느낌</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛없는 우수한 맛 — 딸기초코 등 비린 맛이 없고 음료수처럼 맛있음.
-운동 후 포만감 제공 — 운동 후 섭취하면 은근히 배가 차고 포만감이 생김.
-선물용 인지도 높음 — 운동하는 지인이나 부모님 선물용으로 추천받음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>비린 맛 없는 달콤함 — 단백질 특유의 비린 맛이 없고 일반 음료처럼 맛있음
+든든한 포만감 제공 — 마시고 나면 배가 든든하여 간식 대용으로 유용함
+운동 후 단백질 보충 — 운동 후 한 포씩 챙겨 마시기 편리함</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4234,24 +4217,29 @@
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>배송 누락 발생 — 구성품 수량이 일부 누락되어 수령하는 경우가 발생함</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>이벤트 쿠폰 확인 불편 — 기프티콘 혜택 확인 위치가 불명확함.</t>
+          <t>기프티콘 안내 부족 — 증정 기프티콘 확인 방법에 대한 안내가 불명확함</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>포장 박스 상태 아쉬움 — 배송용 박스 외관 상태가 다소 깨끗하지 않음.
-단일 맛 구성의 아쉬움 — 다양한 맛을 조합한 혼합 상품 옵션이 없음.</t>
+          <t>혼합 구성의 부재 — 여러 맛을 한 번에 맛볼 수 있는 혼합 구성이 없음
+택배 박스 상태 아쉬움 — 배송 박스가 깨끗하지 않은 재활용 상자처럼 도착함</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>배송 누락 및 임의 대체 — 수량 누락과 임의 상품 대체가 발생하고 처리가 늦음.
-강한 간과 가격 부담 — 간이 다소 세고 구성 대비 가격이 비싸게 느껴짐.</t>
+          <t>수량 누락 및 임의 대체 — 수량 불일치 및 사전 고지 없는 대체품 배송으로 스트레스를 유발함
+자극적인 센 간 — 일부 제품의 간이 다소 세게 느껴짐
+배송 중 일부 해동 — 배송 시 제품이 약간 녹아서 도착함</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
@@ -4290,12 +4278,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
           <t>26,900원</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>33,000원</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -4500,7 +4488,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4508,7 +4496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 10정 10일분</t>
+          <t>대웅제약 녹차 카테킨 6정 6일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4523,39 +4511,43 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000282&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/luK3Rb1JJDaCRTymvaHS600000282_00_01luK3Rb1JJDaCRTymvaHS.png</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>896</v>
+        <v>829</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>저렴한 구매 가격 — 다이소 제품이라 가격 부담 없이 구매함.</t>
+          <t>부담 없는 가성비 — 가격이 매우 저렴하여 부담 없이 구매 가능함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>혈당 관리 및 섭취 편의 — 챙겨 먹기 편리하며 혈당 관리에 유용함.</t>
+          <t>하루 한 알 간편 섭취 — 하루 한 알만 챙겨 먹으면 되어 관리가 간편함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>미미한 효과 체감 — 몸의 변화나 효과를 신속하게 체감하기 어려움</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4563,12 +4555,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4578,28 +4570,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627033&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260819/2NKz5YxykngJc58J5cja032627033_00_012NKz5YxykngJc58J5cja.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>375</v>
+        <v>7617</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>간편한 복용법 — 일상에서 간편하게 섭취하기 편리함.</t>
+          <t>뛰어난 가성비 — 가격 대비 만족도가 높아 지속적으로 구매하기 좋음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>빠른 배송과 가성비 — 배송이 빠르고 저렴하여 재구매 의사가 있음.</t>
+          <t>쟁여두기 좋은 품질 — 지인 추천으로 구매할 만큼 만족도가 높아 재구매율이 높음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -4610,7 +4602,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4618,50 +4610,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953530&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/j2jn8GpSpWpVPin1SKu2994953530_00_00j2jn8GpSpWpVPin1SKu2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>249</v>
+        <v>7123</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>피부 컨디션 및 피로 개선 — 꾸준히 먹으면 피부 컨디션과 피로감이 완화됨.</t>
+          <t>꾸준한 간편 섭취 — 매일 챙겨 먹기 쉽고 간편함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>비타민C 결합 성분 — 레티놀과 비타민C를 한 번에 챙길 수 있어 효율적임.</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>위생적인 개별 포장 — 개별 포장되어 있어 외출 시 휴대가 용이함.</t>
-        </is>
-      </c>
+          <t>가벼운 구매 가격 — 매달 저렴하게 구매할 수 있어 부담이 없음</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -4677,12 +4665,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4692,35 +4680,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1737</v>
+        <v>1551</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 100% 유기농 레몬즙을 저렴한 가격에 구매 가능함.</t>
+          <t>상쾌한 이온음료 맛 — 포카리 맛 등 이온음료 맛이 나 거부감 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>편리한 이지컷 소포장 — 소포장되어 이지컷으로 절취하기 편함.</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>다양한 활용성 — 에이드, 샐러드, 음식 요리 등에 두루 활용 가능함.</t>
-        </is>
-      </c>
+          <t>수분 섭취량 증가 — 맹물을 잘 못 마시는 사람도 수분을 쉽게 보충할 수 있음</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -4728,7 +4712,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4736,56 +4720,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000204&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260409/2cHZmOZUJJcZL1ip2bls610910968_00_002cHZmOZUJJcZL1ip2bls.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251121/aHjoRwP9ejVVuu8M0Td4600000204_00_01aHjoRwP9ejVVuu8M0Td4.png</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2651</v>
+        <v>1541</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>뛰어난 가격 가성비 — 유사 성분 제품 대비 가격이 매우 저렴함.</t>
+          <t>숙면 및 피로 회복 — 섭취 후 잠이 잘 오고 피로 회복에 도움이 됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>파인애플 맛 섭취 — 파인애플 맛이 나서 맛이 괜찮음.</t>
+          <t>부담 없는 섭취 제형 — 맹물이 비려 잘 못 마시는 사람도 편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>붓기 효과 체감 미흡 — 실제 붓기 개선 효과를 체감하기 어려움.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>약 특유의 불쾌한 맛 — 약국 약 맛이 느껴져 맛에 대한 호불호가 있음.</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -4799,12 +4775,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4814,34 +4790,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260106/ifUNcDpBRic8ZZffJeay031930043_00_03ifUNcDpBRic8ZZffJeay.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1313</v>
+        <v>2078</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>뛰어난 가격 접근성 — 가격이 매우 저렴하여 시도해보기에 좋음.</t>
+          <t>입면 유도 및 불면 완화 — 취침 전 복용 시 불면증 해소와 빠른 입면에 도움이 됨</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>빠른 배송 속도 — 배송이 빠르고 영양제를 챙기기 용이함.</t>
+          <t>우수한 가성비 — 가격 부담 없이 상비해두기 좋음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>효과 체감의 부족 — 실제 효과를 확실히 체감하기는 다소 부족함.</t>
+          <t>효과의 개인차 존재 — 복용 시 마다 효과에 차이가 있거나 약하게 느껴짐</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -4858,7 +4834,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>대웅제약 커큐민250 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4868,33 +4844,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000314&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20261014/S54HFdVe7PjmJDiYnLDM600000314_00_01S54HFdVe7PjmJDiYnLDM.png</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2414</v>
+        <v>14</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 가격이 저렴하여 매일 챙겨 먹기 부담 없음.</t>
+          <t>정제 형태의 편리함 — 강황 가루와 달리 알약으로 출시되어 먹기 편함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>피로 회복 및 편리성 — 피로 회복에 도움을 주며 복용이 간편함.</t>
+          <t>성분 대비 높은 가성비 — 성분 함량 대비 가격이 저렴함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -4905,7 +4881,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4913,51 +4889,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982831&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/lX1R9GhsEUzz72XUg7VZ611982831_00_00lX1R9GhsEUzz72XUg7VZ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1607</v>
+        <v>371</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 안국약품 루테인을 저렴한 가격에 구매 가능함.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>작은 알약 크기 — 캡슐 크기가 작아 목 넘김과 섭취가 편함.</t>
-        </is>
-      </c>
+          <t>상쾌하고 개운한 느낌 — 섭취 시 입안이 산뜻하고 개운해짐</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>생각보다 큰 알약 — 생각했던 것보다 알약 크기가 크다고 느껴짐.</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -4972,58 +4940,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/y6DqUAmlgLsAXGUrvbmN610910678_00_00y6DqUAmlgLsAXGUrvbmN.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1711</v>
+        <v>896</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>저렴한 관리 비용 — 혈당과 유산균을 저렴한 가격에 함께 관리함.</t>
+          <t>혈당 관리 도움 기대 — 혈당 조절에 도움을 주어 건강 관리에 유용함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>지속적인 재구매 — 가격 부담이 없어 꾸준히 재구매함.</t>
+          <t>저렴한 가성비 — 가격이 저렴하여 부담 없이 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>미흡한 효과 체감 — 한 달 이상 복용해도 효과를 직접 체감하기 어려움.</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5031,49 +4995,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=025575127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953535&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/VsX5iaJon2xHHTs8AQHv025575127_00_01VsX5iaJon2xHHTs8AQHv.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/nv6m1SoKa2Zw57OA3JHL994953535_00_00nv6m1SoKa2Zw57OA3JHL.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>1019</v>
+        <v>1156</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 — 섭취 후 화장실을 잘 가게 되는 효과가 있음.</t>
+          <t>맛있는 음용 제형 — 자몽허니블랙티 맛이라 물에 타서 부담 없이 맛있게 마실 수 있음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 — 가격 대비 매일 식후에 챙겨 먹기 양호함.</t>
+          <t>원활한 배변 활동 — 섭취 후 화장실을 잘 가게 됨</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>체중 감량 효과 미비 — 다이어트 효과는 체감하기 힘듦.</t>
+          <t>미끌거리는 식감 — 맛이 없거나 미끌거려 섭취하기 다소 불편함</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -5190,52 +5154,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -5252,47 +5216,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>이너뷰 바이 리튠</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>홀베리</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>안국약품</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
     </row>
@@ -5304,52 +5268,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 녹차 카테킨 6정 6일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 커큐민250 30정 30일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>홀베리 유기농 레몬즙 10포</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5324,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4.8</v>
@@ -5372,16 +5336,16 @@
         <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
@@ -5397,37 +5361,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
+        <v>829</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>7617</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>7123</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1551</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1541</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>2078</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>371</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>896</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>375</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>249</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1737</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>2651</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>1313</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>2414</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>1607</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>1711</v>
-      </c>
       <c r="L7" s="3" t="n">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5435,102 +5399,90 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 구매 가격 — 다이소 제품이라 가격 부담 없이 구매함.
-혈당 관리 및 섭취 편의 — 챙겨 먹기 편리하며 혈당 관리에 유용함.</t>
+          <t>부담 없는 가성비 — 가격이 매우 저렴하여 부담 없이 구매 가능함
+하루 한 알 간편 섭취 — 하루 한 알만 챙겨 먹으면 되어 관리가 간편함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>간편한 복용법 — 일상에서 간편하게 섭취하기 편리함.
-빠른 배송과 가성비 — 배송이 빠르고 저렴하여 재구매 의사가 있음.</t>
+          <t>뛰어난 가성비 — 가격 대비 만족도가 높아 지속적으로 구매하기 좋음
+쟁여두기 좋은 품질 — 지인 추천으로 구매할 만큼 만족도가 높아 재구매율이 높음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>피부 컨디션 및 피로 개선 — 꾸준히 먹으면 피부 컨디션과 피로감이 완화됨.
-비타민C 결합 성분 — 레티놀과 비타민C를 한 번에 챙길 수 있어 효율적임.
-위생적인 개별 포장 — 개별 포장되어 있어 외출 시 휴대가 용이함.</t>
+          <t>꾸준한 간편 섭취 — 매일 챙겨 먹기 쉽고 간편함
+가벼운 구매 가격 — 매달 저렴하게 구매할 수 있어 부담이 없음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 100% 유기농 레몬즙을 저렴한 가격에 구매 가능함.
-편리한 이지컷 소포장 — 소포장되어 이지컷으로 절취하기 편함.
-다양한 활용성 — 에이드, 샐러드, 음식 요리 등에 두루 활용 가능함.</t>
+          <t>상쾌한 이온음료 맛 — 포카리 맛 등 이온음료 맛이 나 거부감 없이 섭취 가능함
+수분 섭취량 증가 — 맹물을 잘 못 마시는 사람도 수분을 쉽게 보충할 수 있음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가격 가성비 — 유사 성분 제품 대비 가격이 매우 저렴함.
-파인애플 맛 섭취 — 파인애플 맛이 나서 맛이 괜찮음.</t>
+          <t>숙면 및 피로 회복 — 섭취 후 잠이 잘 오고 피로 회복에 도움이 됨
+부담 없는 섭취 제형 — 맹물이 비려 잘 못 마시는 사람도 편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가격 접근성 — 가격이 매우 저렴하여 시도해보기에 좋음.
-빠른 배송 속도 — 배송이 빠르고 영양제를 챙기기 용이함.</t>
+          <t>입면 유도 및 불면 완화 — 취침 전 복용 시 불면증 해소와 빠른 입면에 도움이 됨
+우수한 가성비 — 가격 부담 없이 상비해두기 좋음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 가격이 저렴하여 매일 챙겨 먹기 부담 없음.
-피로 회복 및 편리성 — 피로 회복에 도움을 주며 복용이 간편함.</t>
+          <t>정제 형태의 편리함 — 강황 가루와 달리 알약으로 출시되어 먹기 편함
+성분 대비 높은 가성비 — 성분 함량 대비 가격이 저렴함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 안국약품 루테인을 저렴한 가격에 구매 가능함.
-작은 알약 크기 — 캡슐 크기가 작아 목 넘김과 섭취가 편함.</t>
+          <t>상쾌하고 개운한 느낌 — 섭취 시 입안이 산뜻하고 개운해짐</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 관리 비용 — 혈당과 유산균을 저렴한 가격에 함께 관리함.
-지속적인 재구매 — 가격 부담이 없어 꾸준히 재구매함.</t>
+          <t>혈당 관리 도움 기대 — 혈당 조절에 도움을 주어 건강 관리에 유용함
+저렴한 가성비 — 가격이 저렴하여 부담 없이 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 — 섭취 후 화장실을 잘 가게 되는 효과가 있음.
-부담 없는 가성비 — 가격 대비 매일 식후에 챙겨 먹기 양호함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>맛있는 음용 제형 — 자몽허니블랙티 맛이라 물에 타서 부담 없이 맛있게 마실 수 있음
+원활한 배변 활동 — 섭취 후 화장실을 잘 가게 됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>미미한 효과 체감 — 몸의 변화나 효과를 신속하게 체감하기 어려움</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>붓기 효과 체감 미흡 — 실제 붓기 개선 효과를 체감하기 어려움.
-약 특유의 불쾌한 맛 — 약국 약 맛이 느껴져 맛에 대한 호불호가 있음.</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>효과 체감의 부족 — 실제 효과를 확실히 체감하기는 다소 부족함.</t>
+          <t>효과의 개인차 존재 — 복용 시 마다 효과에 차이가 있거나 약하게 느껴짐</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>생각보다 큰 알약 — 생각했던 것보다 알약 크기가 크다고 느껴짐.</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>미흡한 효과 체감 — 한 달 이상 복용해도 효과를 직접 체감하기 어려움.</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>체중 감량 효과 미비 — 다이어트 효과는 체감하기 힘듦.</t>
+          <t>미끌거리는 식감 — 맛이 없거나 미끌거려 섭취하기 다소 불편함</t>
         </is>
       </c>
     </row>
@@ -5552,42 +5504,42 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5712,16 +5664,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>36.7</v>
+        <v>33.3</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -5731,16 +5683,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -5765,26 +5717,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5822,7 +5774,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5836,6 +5788,25 @@
       </c>
       <c r="E8" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
